--- a/planogram/MAHSAN 8.xlsx
+++ b/planogram/MAHSAN 8.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sverdlik\Desktop\WORKSPACE\PLANOGRAM MAHSAN FORMULA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A4F34D-EA99-4A75-AB50-001F1EC29545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8ED299-5AA5-487A-BF57-2BCDAB3490F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" xr2:uid="{4C13ED5E-5E73-435F-87B6-8A790C6A2201}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14160" activeTab="1" xr2:uid="{4C13ED5E-5E73-435F-87B6-8A790C6A2201}"/>
   </bookViews>
   <sheets>
     <sheet name="MAHSAN דגים" sheetId="4" r:id="rId1"/>
@@ -45,7 +45,7 @@
     <author>Dan Sverdlik</author>
   </authors>
   <commentList>
-    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{4C50291D-D90B-4776-864E-36D00E3B1EAA}">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{03F2474D-511C-4F13-B4B7-DCD6A3F987AC}">
       <text>
         <r>
           <rPr>
@@ -562,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
@@ -591,110 +591,105 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,144 +1019,144 @@
   <sheetData>
     <row r="2" spans="3:31" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="56"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="66" t="s">
+      <c r="C3" s="34"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="66"/>
-      <c r="T3" s="66"/>
-      <c r="U3" s="66"/>
-      <c r="V3" s="66"/>
-      <c r="W3" s="66"/>
-      <c r="X3" s="66"/>
-      <c r="Y3" s="66"/>
-      <c r="Z3" s="66"/>
-      <c r="AA3" s="66"/>
-      <c r="AB3" s="66"/>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="67"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="50"/>
     </row>
     <row r="4" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="59"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="61"/>
-      <c r="N4" s="48" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="48"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="48"/>
-      <c r="S4" s="48"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="48"/>
-      <c r="V4" s="48"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="48"/>
-      <c r="Y4" s="48"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="48"/>
-      <c r="AB4" s="48"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="49"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
+      <c r="W4" s="41"/>
+      <c r="X4" s="41"/>
+      <c r="Y4" s="41"/>
+      <c r="Z4" s="41"/>
+      <c r="AA4" s="41"/>
+      <c r="AB4" s="41"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="42"/>
     </row>
     <row r="5" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="59"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="61"/>
-      <c r="N5" s="48" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="48"/>
-      <c r="V5" s="48"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="48"/>
-      <c r="Y5" s="48"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="48"/>
-      <c r="AB5" s="48"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="49"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
+      <c r="W5" s="41"/>
+      <c r="X5" s="41"/>
+      <c r="Y5" s="41"/>
+      <c r="Z5" s="41"/>
+      <c r="AA5" s="41"/>
+      <c r="AB5" s="41"/>
+      <c r="AC5" s="41"/>
+      <c r="AD5" s="42"/>
     </row>
     <row r="6" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="59"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="47"/>
-      <c r="AA6" s="47"/>
-      <c r="AB6" s="47"/>
-      <c r="AC6" s="47"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
       <c r="AD6" s="17"/>
     </row>
     <row r="7" spans="3:31" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="52"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="31"/>
       <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -1196,33 +1191,33 @@
       <c r="AD7" s="17"/>
     </row>
     <row r="8" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="55">
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33">
         <v>56</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="33">
         <v>55</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="33">
         <v>54</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="33">
         <v>50</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="33">
         <v>49</v>
       </c>
-      <c r="J8" s="55">
+      <c r="J8" s="33">
         <v>48</v>
       </c>
-      <c r="K8" s="55">
+      <c r="K8" s="33">
         <v>47</v>
       </c>
-      <c r="L8" s="55">
+      <c r="L8" s="33">
         <v>46</v>
       </c>
-      <c r="M8" s="55">
+      <c r="M8" s="33">
         <v>45</v>
       </c>
       <c r="N8" s="16">
@@ -1277,34 +1272,34 @@
     </row>
     <row r="9" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="1"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
-      <c r="U9" s="47"/>
-      <c r="V9" s="47"/>
-      <c r="W9" s="47"/>
-      <c r="X9" s="47"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
-      <c r="AA9" s="47"/>
-      <c r="AB9" s="47"/>
-      <c r="AC9" s="47"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
       <c r="AD9" s="17"/>
-      <c r="AE9" s="29" t="s">
+      <c r="AE9" s="52" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1338,20 +1333,20 @@
       <c r="M10" s="16">
         <v>41</v>
       </c>
-      <c r="N10" s="50">
+      <c r="N10" s="29">
         <v>40</v>
       </c>
-      <c r="O10" s="50">
+      <c r="O10" s="29">
         <v>39</v>
       </c>
-      <c r="P10" s="50">
+      <c r="P10" s="29">
         <v>38</v>
       </c>
-      <c r="Q10" s="50">
+      <c r="Q10" s="29">
         <v>37</v>
       </c>
-      <c r="R10" s="47"/>
-      <c r="S10" s="51">
+      <c r="R10" s="28"/>
+      <c r="S10" s="30">
         <v>30</v>
       </c>
       <c r="T10" s="16">
@@ -1384,14 +1379,14 @@
       <c r="AC10" s="16">
         <v>10</v>
       </c>
-      <c r="AD10" s="68">
+      <c r="AD10" s="39">
         <v>9</v>
       </c>
-      <c r="AE10" s="29"/>
+      <c r="AE10" s="52"/>
     </row>
     <row r="11" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="69"/>
-      <c r="D11" s="65"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="38"/>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16"/>
@@ -1405,7 +1400,7 @@
       <c r="O11" s="16"/>
       <c r="P11" s="16"/>
       <c r="Q11" s="16"/>
-      <c r="R11" s="47"/>
+      <c r="R11" s="28"/>
       <c r="S11" s="16"/>
       <c r="T11" s="16"/>
       <c r="U11" s="16"/>
@@ -1417,157 +1412,157 @@
       <c r="AA11" s="16"/>
       <c r="AB11" s="16"/>
       <c r="AC11" s="16"/>
-      <c r="AD11" s="68"/>
-      <c r="AE11" s="29"/>
+      <c r="AD11" s="39"/>
+      <c r="AE11" s="52"/>
     </row>
     <row r="12" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="1"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
-      <c r="U12" s="47"/>
-      <c r="V12" s="47"/>
-      <c r="W12" s="47"/>
-      <c r="X12" s="47"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
-      <c r="AA12" s="47"/>
-      <c r="AB12" s="47"/>
-      <c r="AC12" s="47"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
       <c r="AD12" s="17"/>
-      <c r="AE12" s="28"/>
+      <c r="AE12" s="51"/>
     </row>
     <row r="13" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="53"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="48" t="s">
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
+      <c r="J13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="46"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="Y13" s="48"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="48"/>
-      <c r="AB13" s="48"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="49"/>
-      <c r="AE13" s="28"/>
+      <c r="Y13" s="41"/>
+      <c r="Z13" s="41"/>
+      <c r="AA13" s="41"/>
+      <c r="AB13" s="41"/>
+      <c r="AC13" s="41"/>
+      <c r="AD13" s="42"/>
+      <c r="AE13" s="51"/>
     </row>
     <row r="14" spans="3:31" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="48" t="s">
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="Y14" s="48"/>
-      <c r="Z14" s="48"/>
-      <c r="AA14" s="48"/>
-      <c r="AB14" s="48"/>
-      <c r="AC14" s="48"/>
-      <c r="AD14" s="49"/>
-      <c r="AE14" s="28"/>
+      <c r="Y14" s="41"/>
+      <c r="Z14" s="41"/>
+      <c r="AA14" s="41"/>
+      <c r="AB14" s="41"/>
+      <c r="AC14" s="41"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="51"/>
     </row>
     <row r="15" spans="3:31" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="72"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="72"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="72"/>
-      <c r="I15" s="72"/>
-      <c r="J15" s="72"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="72"/>
-      <c r="N15" s="72"/>
-      <c r="O15" s="72"/>
-      <c r="P15" s="72"/>
-      <c r="Q15" s="72"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
-      <c r="X15" s="73" t="s">
+      <c r="X15" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="Y15" s="73"/>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="73"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="74"/>
+      <c r="Y15" s="43"/>
+      <c r="Z15" s="43"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="43"/>
+      <c r="AD15" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="N3:AD3"/>
+    <mergeCell ref="N4:AD4"/>
+    <mergeCell ref="N5:AD5"/>
+    <mergeCell ref="AE12:AE14"/>
+    <mergeCell ref="AE9:AE11"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="X14:AD14"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="C13:Q13"/>
     <mergeCell ref="C14:Q14"/>
     <mergeCell ref="C15:Q15"/>
-    <mergeCell ref="N3:AD3"/>
-    <mergeCell ref="N4:AD4"/>
-    <mergeCell ref="N5:AD5"/>
-    <mergeCell ref="AE12:AE14"/>
-    <mergeCell ref="AE9:AE11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="35" orientation="portrait" r:id="rId1"/>
@@ -1587,39 +1582,39 @@
   <sheetData>
     <row r="1" spans="2:16" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
       <c r="P2" s="12"/>
     </row>
     <row r="3" spans="2:16" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="36"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
       <c r="P3" s="13"/>
     </row>
     <row r="4" spans="2:16" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -1840,44 +1835,44 @@
     <row r="11" spans="2:16" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="40"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="63"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="38"/>
+      <c r="N11" s="60"/>
+      <c r="O11" s="61"/>
       <c r="P11" s="13"/>
     </row>
     <row r="12" spans="2:16" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="66"/>
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="43"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
       <c r="P12" s="15"/>
     </row>
     <row r="13" spans="2:16" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="34"/>
+      <c r="C13" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -1899,7 +1894,7 @@
     <mergeCell ref="D12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1990,7 +1985,7 @@
       </c>
     </row>
     <row r="4" spans="1:20" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="69" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="4"/>
@@ -2015,7 +2010,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -2038,7 +2033,7 @@
       </c>
     </row>
     <row r="6" spans="1:20" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -2175,7 +2170,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="13"/>
-      <c r="T9" s="45"/>
+      <c r="T9" s="68"/>
     </row>
     <row r="10" spans="1:20" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
@@ -2196,7 +2191,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="13"/>
-      <c r="T10" s="45"/>
+      <c r="T10" s="68"/>
     </row>
     <row r="11" spans="1:20" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
@@ -2217,7 +2212,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="13"/>
-      <c r="T11" s="45"/>
+      <c r="T11" s="68"/>
     </row>
     <row r="12" spans="1:20" ht="31.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
